--- a/data/CReDEs/jy/jy_ssjl.xlsx
+++ b/data/CReDEs/jy/jy_ssjl.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\九院-标准化\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\九院-标准化\CRedes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280AD389-6474-4CE3-B0C7-0DAC2E6D551F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90556539-078C-41AD-85F2-45FB1FC7728A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11805" xr2:uid="{983BBB82-CA77-4EF9-A65D-AEA8829627CD}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="57">
   <si>
     <t>标签名称</t>
   </si>
@@ -204,6 +204,14 @@
   </si>
   <si>
     <t>是， 否</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ml</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -626,7 +634,9 @@
       <c r="E2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -884,7 +894,9 @@
       <c r="E16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
@@ -914,5 +926,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>